--- a/BioVision_Performance_Metrics.xlsx
+++ b/BioVision_Performance_Metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnasO\Documents\GitHub\BioVision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5006B4D9-9EFA-41C4-8F81-EED1F6EDB386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224FF596-8BD7-4D04-8EC5-3576A155F74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="1400" windowWidth="19200" windowHeight="11170" xr2:uid="{6BBA70F4-AE0C-415B-888C-8F32E744E39D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6BBA70F4-AE0C-415B-888C-8F32E744E39D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="97">
   <si>
     <t>Biological Target</t>
   </si>
@@ -312,54 +312,6 @@
   </si>
   <si>
     <t>37.94% (95% CI: [36.44%, 39.44%])</t>
-  </si>
-  <si>
-    <t>Basophil</t>
-  </si>
-  <si>
-    <t>Eosinophil</t>
-  </si>
-  <si>
-    <t>Lymphocyte</t>
-  </si>
-  <si>
-    <t>Monocyte</t>
-  </si>
-  <si>
-    <t>Neutrophil</t>
-  </si>
-  <si>
-    <t>100.00% (95% CI: [97.67%, 100.00%])</t>
-  </si>
-  <si>
-    <t>99.69% (95% CI: [98.25%, 99.94%])</t>
-  </si>
-  <si>
-    <t>99.37% (95% CI: [96.50%, 99.89%])</t>
-  </si>
-  <si>
-    <t>100.00% (95% CI: [89.57%, 100.00%])</t>
-  </si>
-  <si>
-    <t>98.21% (95% CI: [90.55%, 99.68%])</t>
-  </si>
-  <si>
-    <t>Brain Tumor</t>
-  </si>
-  <si>
-    <t>Healthy</t>
-  </si>
-  <si>
-    <t>Breast Cancer</t>
-  </si>
-  <si>
-    <t>100.00% (95% CI: [100.00%, 100.00%])</t>
-  </si>
-  <si>
-    <t>76.92% (95% CI: [50.42%, 103.42%])</t>
-  </si>
-  <si>
-    <t>Classification Performance BioVision (F1-Score [95% CI])</t>
   </si>
   <si>
     <t>Pancreas (Mouse model)</t>
@@ -504,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -563,9 +515,6 @@
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -934,13 +883,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{060E00A1-6148-44B1-AC09-A99E219A8EA6}">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="11"/>
-    <col min="2" max="2" width="20" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.90625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.90625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.90625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.26953125" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.7265625" style="12" customWidth="1"/>
     <col min="7" max="7" width="6.08984375" style="12" bestFit="1" customWidth="1"/>
@@ -948,7 +897,7 @@
     <col min="11" max="16384" width="8.7265625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.35">
       <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
@@ -964,16 +913,10 @@
       <c r="F1" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
-        <v>112</v>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="8"/>
@@ -982,24 +925,12 @@
       <c r="F2" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="22">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -1014,24 +945,12 @@
       <c r="F3" s="13">
         <v>0.95709999999999995</v>
       </c>
-      <c r="G3" s="22">
-        <v>1</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="22">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="21">
         <v>2</v>
       </c>
-      <c r="B4" s="31"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1044,24 +963,12 @@
       <c r="F4" s="13">
         <v>0.99360000000000004</v>
       </c>
-      <c r="G4" s="22">
-        <v>2</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="22">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="21">
         <v>3</v>
       </c>
-      <c r="B5" s="31"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
@@ -1074,24 +981,12 @@
       <c r="F5" s="13">
         <v>0.98</v>
       </c>
-      <c r="G5" s="22">
-        <v>3</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="22">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="21">
         <v>4</v>
       </c>
-      <c r="B6" s="31"/>
+      <c r="B6" s="30"/>
       <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
@@ -1104,24 +999,12 @@
       <c r="F6" s="13">
         <v>0.94389999999999996</v>
       </c>
-      <c r="G6" s="22">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="22">
-        <v>5</v>
-      </c>
-      <c r="B7" s="31"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="21">
+        <v>5</v>
+      </c>
+      <c r="B7" s="30"/>
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1134,24 +1017,12 @@
       <c r="F7" s="13">
         <v>1</v>
       </c>
-      <c r="G7" s="22">
-        <v>5</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="22">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="21">
         <v>6</v>
       </c>
-      <c r="B8" s="31"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1164,24 +1035,12 @@
       <c r="F8" s="13">
         <v>1</v>
       </c>
-      <c r="G8" s="22">
-        <v>6</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="22">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="21">
         <v>7</v>
       </c>
-      <c r="B9" s="31"/>
+      <c r="B9" s="30"/>
       <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
@@ -1194,24 +1053,12 @@
       <c r="F9" s="13">
         <v>0.97619999999999996</v>
       </c>
-      <c r="G9" s="22">
-        <v>7</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="22">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="21">
         <v>8</v>
       </c>
-      <c r="B10" s="31"/>
+      <c r="B10" s="30"/>
       <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
@@ -1224,24 +1071,12 @@
       <c r="F10" s="13">
         <v>1</v>
       </c>
-      <c r="G10" s="22">
-        <v>8</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="22">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="21">
         <v>9</v>
       </c>
-      <c r="B11" s="31"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="3" t="s">
         <v>21</v>
       </c>
@@ -1254,24 +1089,12 @@
       <c r="F11" s="13">
         <v>0.99150000000000005</v>
       </c>
-      <c r="G11" s="22">
-        <v>9</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="22">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="21">
         <v>10</v>
       </c>
-      <c r="B12" s="31"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
@@ -1284,24 +1107,12 @@
       <c r="F12" s="13">
         <v>0.94069999999999998</v>
       </c>
-      <c r="G12" s="22">
-        <v>10</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="22">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="21">
         <v>11</v>
       </c>
-      <c r="B13" s="31"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="3" t="s">
         <v>23</v>
       </c>
@@ -1314,24 +1125,12 @@
       <c r="F13" s="13">
         <v>0.98460000000000003</v>
       </c>
-      <c r="G13" s="22">
-        <v>11</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="22">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="21">
         <v>12</v>
       </c>
-      <c r="B14" s="31"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="3" t="s">
         <v>24</v>
       </c>
@@ -1344,24 +1143,12 @@
       <c r="F14" s="13">
         <v>0.95240000000000002</v>
       </c>
-      <c r="G14" s="22">
-        <v>12</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="22">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="21">
         <v>13</v>
       </c>
-      <c r="B15" s="31"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
@@ -1374,24 +1161,12 @@
       <c r="F15" s="13">
         <v>1</v>
       </c>
-      <c r="G15" s="22">
-        <v>13</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="22">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="21">
         <v>14</v>
       </c>
-      <c r="B16" s="31"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="3" t="s">
         <v>26</v>
       </c>
@@ -1404,24 +1179,12 @@
       <c r="F16" s="13">
         <v>1</v>
       </c>
-      <c r="G16" s="22">
-        <v>14</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="22">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="21">
         <v>15</v>
       </c>
-      <c r="B17" s="31"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
@@ -1434,26 +1197,14 @@
       <c r="F17" s="13">
         <v>1</v>
       </c>
-      <c r="G17" s="22">
-        <v>15</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="22">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="21">
         <v>16</v>
       </c>
-      <c r="B18" s="31"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="3" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>5</v>
@@ -1464,24 +1215,12 @@
       <c r="F18" s="13">
         <v>1</v>
       </c>
-      <c r="G18" s="22">
-        <v>16</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" s="22">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="21">
         <v>17</v>
       </c>
-      <c r="B19" s="32"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="6" t="s">
         <v>12</v>
       </c>
@@ -1494,21 +1233,9 @@
       <c r="F19" s="20">
         <v>0.99590000000000001</v>
       </c>
-      <c r="G19" s="22">
-        <v>17</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="J19" s="23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="22">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="21">
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1526,21 +1253,9 @@
       <c r="F20" s="5">
         <v>1</v>
       </c>
-      <c r="G20" s="22">
-        <v>18</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="22">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="21">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1558,21 +1273,9 @@
       <c r="F21" s="5">
         <v>1</v>
       </c>
-      <c r="G21" s="22">
-        <v>19</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="22">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="21">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1590,221 +1293,348 @@
       <c r="F22" s="5">
         <v>1</v>
       </c>
-      <c r="G22" s="22">
-        <v>20</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.35">
-      <c r="B25" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="21"/>
-      <c r="E26" s="25"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E25" s="24"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="25"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E26" s="24"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="26"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B27" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E27" s="25"/>
+      <c r="H26" s="25"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="23"/>
+      <c r="B27" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="24"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="26"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B28" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="25"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="26"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H27" s="25"/>
+    </row>
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.35">
+      <c r="A28" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="24"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="25"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="21">
+        <v>1</v>
+      </c>
       <c r="B29" s="10" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="26"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="24"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="25"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="21">
+        <v>2</v>
+      </c>
       <c r="B30" s="10" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="26"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="24"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="25"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="21">
+        <v>3</v>
+      </c>
       <c r="B31" s="10" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="26"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B32" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="E32" s="25"/>
+        <v>38</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="24"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="25"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="21">
+        <v>4</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="24"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="26"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H32" s="25"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="21">
+        <v>5</v>
+      </c>
       <c r="B33" s="10" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="26"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="21">
+        <v>6</v>
+      </c>
       <c r="B34" s="10" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="26"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="21">
+        <v>7</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="21">
+        <v>8</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="21">
+        <v>9</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="21">
         <v>10</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="26"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B36" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="26"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B37" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="26"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E38" s="25"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="26"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E39" s="25"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="26"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E40" s="25"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="26"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E41" s="25"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="26"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E42" s="25"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="26"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E43" s="25"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="26"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E44" s="25"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="26"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E45" s="25"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="26"/>
+      <c r="B38" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="21">
+        <v>11</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="21">
+        <v>12</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="21">
+        <v>13</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="21">
+        <v>14</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="21">
+        <v>15</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="21">
+        <v>16</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="21">
+        <v>17</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="21">
+        <v>18</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="21">
+        <v>19</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="21">
+        <v>20</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="E25:H25"/>
+  <mergeCells count="2">
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B3:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/BioVision_Performance_Metrics.xlsx
+++ b/BioVision_Performance_Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnasO\Documents\GitHub\BioVision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C18F72-A994-40DD-88E3-773BEAB63225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4080AF-C19B-44BA-8FC8-F1A77875C4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6BBA70F4-AE0C-415B-888C-8F32E744E39D}"/>
   </bookViews>
@@ -35,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>Biological Target</t>
   </si>
@@ -381,6 +403,9 @@
   </si>
   <si>
     <t>Roboflow Universe (https://universe.roboflow.com), a public platform for computer vision datasets.</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
@@ -511,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -522,69 +547,73 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -920,10 +949,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E31BC63-FA3A-471A-9E02-568C0CB41883}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="33.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.08984375" bestFit="1" customWidth="1"/>
@@ -931,388 +960,388 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33" x14ac:dyDescent="0.35">
-      <c r="A1" s="6"/>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="10">
+      <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="13">
+      <c r="D4" s="8"/>
+      <c r="E4" s="10">
         <v>520</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="11">
         <v>0.95709999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
+      <c r="A5" s="7">
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8">
         <v>617</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="11">
         <v>0.99360000000000004</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="10">
+      <c r="A6" s="7">
         <v>3</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="24"/>
+      <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="13">
+      <c r="D6" s="8"/>
+      <c r="E6" s="10">
         <v>500</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="11">
         <v>0.98</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
+      <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="24"/>
+      <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="13">
+      <c r="D7" s="8"/>
+      <c r="E7" s="10">
         <v>513</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="11">
         <v>0.94389999999999996</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="10">
+      <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="24"/>
+      <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="13">
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
         <v>542</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
+      <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="24"/>
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="13">
+      <c r="D9" s="8"/>
+      <c r="E9" s="10">
         <v>453</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="10">
+      <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="12" t="s">
+      <c r="B10" s="24"/>
+      <c r="C10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="13">
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
         <v>340</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="11">
         <v>0.97619999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="10">
+      <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="12" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="10">
         <v>461</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="10">
+      <c r="A12" s="7">
         <v>9</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="24"/>
+      <c r="C12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="8">
         <v>490</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="11">
         <v>0.99150000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="10">
+      <c r="A13" s="7">
         <v>10</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="12" t="s">
+      <c r="B13" s="24"/>
+      <c r="C13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="13">
+      <c r="D13" s="13"/>
+      <c r="E13" s="10">
         <v>497</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="11">
         <v>0.94069999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="10">
+      <c r="A14" s="7">
         <v>11</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="12" t="s">
+      <c r="B14" s="24"/>
+      <c r="C14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="13">
+      <c r="D14" s="13"/>
+      <c r="E14" s="10">
         <v>698</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="11">
         <v>0.98460000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="10">
+      <c r="A15" s="7">
         <v>12</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="12" t="s">
+      <c r="B15" s="24"/>
+      <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="13">
+      <c r="D15" s="13"/>
+      <c r="E15" s="10">
         <v>393</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="11">
         <v>0.95240000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="10">
+      <c r="A16" s="7">
         <v>13</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="24"/>
+      <c r="C16" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="13">
+      <c r="D16" s="13"/>
+      <c r="E16" s="10">
         <v>498</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="10">
+      <c r="A17" s="7">
         <v>14</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="12" t="s">
+      <c r="B17" s="24"/>
+      <c r="C17" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="13">
+      <c r="D17" s="13"/>
+      <c r="E17" s="10">
         <v>215</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="10">
+      <c r="A18" s="7">
         <v>15</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="12" t="s">
+      <c r="B18" s="24"/>
+      <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="13">
+      <c r="D18" s="13"/>
+      <c r="E18" s="10">
         <v>231</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A19" s="10">
+      <c r="A19" s="7">
         <v>16</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="12" t="s">
+      <c r="B19" s="24"/>
+      <c r="C19" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="10">
         <v>1656</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="10">
+      <c r="A20" s="7">
         <v>17</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="18" t="s">
+      <c r="B20" s="24"/>
+      <c r="C20" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="15">
         <v>37695</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="11">
         <v>0.99590000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="10">
+      <c r="A21" s="7">
         <v>18</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="11">
+      <c r="D21" s="23"/>
+      <c r="E21" s="8">
         <v>846</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="10">
+      <c r="A22" s="7">
         <v>19</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="20">
+      <c r="D22" s="23"/>
+      <c r="E22" s="15">
         <v>4488</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="10">
+      <c r="A23" s="7">
         <v>20</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20">
+      <c r="D23" s="23"/>
+      <c r="E23" s="15">
         <v>13059</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
     </row>
     <row r="27" spans="1:6" ht="45" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
@@ -1329,295 +1358,312 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="22">
+      <c r="A28" s="17">
         <v>1</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="22">
+      <c r="A29" s="17">
         <v>2</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="18" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="22">
+      <c r="A30" s="17">
         <v>3</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="22">
+      <c r="A31" s="17">
         <v>4</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="22">
+      <c r="A32" s="17">
         <v>5</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="22">
+      <c r="A33" s="17">
         <v>6</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="22">
+      <c r="A34" s="17">
         <v>7</v>
       </c>
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="22">
+      <c r="A35" s="17">
         <v>8</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="18" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="22">
+      <c r="A36" s="17">
         <v>9</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="22">
+      <c r="A37" s="17">
         <v>10</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="22">
+      <c r="A38" s="17">
         <v>11</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="22">
+      <c r="A39" s="17">
         <v>12</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="D39" s="18" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="22">
+      <c r="A40" s="17">
         <v>13</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="23" t="s">
+      <c r="D40" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="22">
+      <c r="A41" s="17">
         <v>14</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="D41" s="18" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="22">
+      <c r="A42" s="17">
         <v>15</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="18" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="22">
+      <c r="A43" s="17">
         <v>16</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C43" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="22">
+      <c r="A44" s="17">
         <v>17</v>
       </c>
-      <c r="B44" s="24" t="s">
+      <c r="B44" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D44" s="24" t="s">
+      <c r="D44" s="19" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="22">
+      <c r="A45" s="17">
         <v>18</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="23" t="s">
+      <c r="D45" s="18" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="22">
+      <c r="A46" s="17">
         <v>19</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D46" s="18" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="22">
+      <c r="A47" s="17">
         <v>20</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="18" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="25" t="str" cm="1">
+        <f t="array" ref="B50">TEXT(AVERAGE(VALUE(LEFT(B28:B47,FIND("%",B28:B47)-1))),"0.00")&amp;"% (95% CI: ["&amp;TEXT(AVERAGE(VALUE(MID(B28:B47,FIND("[",B28:B47)+1,FIND("%",B28:B47,FIND("[",B28:B47))-FIND("[",B28:B47)-1))),"0.00")&amp;"%, "&amp;TEXT(AVERAGE(VALUE(MID(B28:B47,FIND(", ",B28:B47,FIND("[",B28:B47))+2,FIND("%]",B28:B47)-FIND(", ",B28:B47,FIND("[",B28:B47))-2))),"0.00")&amp;"%])"</f>
+        <v>94.79% (95% CI: [93.51%, 96.08%])</v>
+      </c>
+      <c r="C50" s="25" t="str" cm="1">
+        <f t="array" ref="C50">TEXT(AVERAGE(VALUE(LEFT(C28:C47,FIND("%",C28:C47)-1))),"0.00")&amp;"% (95% CI: ["&amp;TEXT(AVERAGE(VALUE(MID(C28:C47,FIND("[",C28:C47)+1,FIND("%",C28:C47,FIND("[",C28:C47))-FIND("[",C28:C47)-1))),"0.00")&amp;"%, "&amp;TEXT(AVERAGE(VALUE(MID(C28:C47,FIND(", ",C28:C47,FIND("[",C28:C47))+2,FIND("%]",C28:C47)-FIND(", ",C28:C47,FIND("[",C28:C47))-2))),"0.00")&amp;"%])"</f>
+        <v>36.55% (95% CI: [22.71%, 50.40%])</v>
+      </c>
+      <c r="D50" s="25" t="str" cm="1">
+        <f t="array" ref="D50">TEXT(AVERAGE(VALUE(LEFT(D28:D47,FIND("%",D28:D47)-1))),"0.00")&amp;"% (95% CI: ["&amp;TEXT(AVERAGE(VALUE(MID(D28:D47,FIND("[",D28:D47)+1,FIND("%",D28:D47,FIND("[",D28:D47))-FIND("[",D28:D47)-1))),"0.00")&amp;"%, "&amp;TEXT(AVERAGE(VALUE(MID(D28:D47,FIND(", ",D28:D47,FIND("[",D28:D47))+2,FIND("%]",D28:D47)-FIND(", ",D28:D47,FIND("[",D28:D47))-2))),"0.00")&amp;"%])"</f>
+        <v>25.04% (95% CI: [14.95%, 35.13%])</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="B5:B20"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="B5:B20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D12" r:id="rId1" display="https://gtexportal.org/home/histologyPage" xr:uid="{8E7AA31D-7222-4846-988C-D886EC642037}"/>
@@ -1625,5 +1671,6 @@
     <hyperlink ref="D20" r:id="rId3" display="https://universe.roboflow.com/" xr:uid="{43CF4427-DBF6-49A2-A5AB-7F7230077706}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
 </worksheet>
 </file>
--- a/BioVision_Performance_Metrics.xlsx
+++ b/BioVision_Performance_Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnasO\Documents\GitHub\BioVision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4080AF-C19B-44BA-8FC8-F1A77875C4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569CAF31-AF14-4C90-A2DF-D3584D701DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6BBA70F4-AE0C-415B-888C-8F32E744E39D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
   <si>
     <t>Biological Target</t>
   </si>
@@ -536,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -595,25 +595,28 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1335,15 +1338,24 @@
         <v>1</v>
       </c>
     </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E24" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="27">
+        <f>AVERAGE(F4:F23)</f>
+        <v>0.98579500000000009</v>
+      </c>
+    </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-    </row>
-    <row r="27" spans="1:6" ht="45" x14ac:dyDescent="0.35">
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+    </row>
+    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>90</v>
       </c>
@@ -1638,18 +1650,18 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B50" s="25" t="str" cm="1">
+      <c r="B50" s="20" t="str" cm="1">
         <f t="array" ref="B50">TEXT(AVERAGE(VALUE(LEFT(B28:B47,FIND("%",B28:B47)-1))),"0.00")&amp;"% (95% CI: ["&amp;TEXT(AVERAGE(VALUE(MID(B28:B47,FIND("[",B28:B47)+1,FIND("%",B28:B47,FIND("[",B28:B47))-FIND("[",B28:B47)-1))),"0.00")&amp;"%, "&amp;TEXT(AVERAGE(VALUE(MID(B28:B47,FIND(", ",B28:B47,FIND("[",B28:B47))+2,FIND("%]",B28:B47)-FIND(", ",B28:B47,FIND("[",B28:B47))-2))),"0.00")&amp;"%])"</f>
         <v>94.79% (95% CI: [93.51%, 96.08%])</v>
       </c>
-      <c r="C50" s="25" t="str" cm="1">
+      <c r="C50" s="20" t="str" cm="1">
         <f t="array" ref="C50">TEXT(AVERAGE(VALUE(LEFT(C28:C47,FIND("%",C28:C47)-1))),"0.00")&amp;"% (95% CI: ["&amp;TEXT(AVERAGE(VALUE(MID(C28:C47,FIND("[",C28:C47)+1,FIND("%",C28:C47,FIND("[",C28:C47))-FIND("[",C28:C47)-1))),"0.00")&amp;"%, "&amp;TEXT(AVERAGE(VALUE(MID(C28:C47,FIND(", ",C28:C47,FIND("[",C28:C47))+2,FIND("%]",C28:C47)-FIND(", ",C28:C47,FIND("[",C28:C47))-2))),"0.00")&amp;"%])"</f>
         <v>36.55% (95% CI: [22.71%, 50.40%])</v>
       </c>
-      <c r="D50" s="25" t="str" cm="1">
+      <c r="D50" s="20" t="str" cm="1">
         <f t="array" ref="D50">TEXT(AVERAGE(VALUE(LEFT(D28:D47,FIND("%",D28:D47)-1))),"0.00")&amp;"% (95% CI: ["&amp;TEXT(AVERAGE(VALUE(MID(D28:D47,FIND("[",D28:D47)+1,FIND("%",D28:D47,FIND("[",D28:D47))-FIND("[",D28:D47)-1))),"0.00")&amp;"%, "&amp;TEXT(AVERAGE(VALUE(MID(D28:D47,FIND(", ",D28:D47,FIND("[",D28:D47))+2,FIND("%]",D28:D47)-FIND(", ",D28:D47,FIND("[",D28:D47))-2))),"0.00")&amp;"%])"</f>
         <v>25.04% (95% CI: [14.95%, 35.13%])</v>
       </c>

--- a/BioVision_Performance_Metrics.xlsx
+++ b/BioVision_Performance_Metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnasO\Documents\GitHub\BioVision\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnasO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569CAF31-AF14-4C90-A2DF-D3584D701DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1E0E63-6434-41A6-9772-1C02B58A8F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6BBA70F4-AE0C-415B-888C-8F32E744E39D}"/>
   </bookViews>
@@ -35,30 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>Biological Target</t>
   </si>
@@ -135,199 +113,7 @@
     <t>kidney cortex</t>
   </si>
   <si>
-    <t>VGG16 (Zero-Shot)</t>
-  </si>
-  <si>
-    <t>EfficientNet-B0 (Zero-Shot)</t>
-  </si>
-  <si>
-    <t>BioVision (Fine-Tuned)</t>
-  </si>
-  <si>
-    <t>90.96% (95% CI: [88.74%, 93.18%])</t>
-  </si>
-  <si>
-    <t>39.33% (95% CI: [27.16%, 51.51%])</t>
-  </si>
-  <si>
-    <t>20.24% (95% CI: [12.23%, 28.25%])</t>
-  </si>
-  <si>
-    <t>95.73% (95% CI: [95.52%, 95.94%])</t>
-  </si>
-  <si>
-    <t>54.72% (95% CI: [41.62%, 67.83%])</t>
-  </si>
-  <si>
-    <t>31.14% (95% CI: [19.55%, 42.73%])</t>
-  </si>
-  <si>
-    <t>94.18% (95% CI: [93.64%, 94.73%])</t>
-  </si>
-  <si>
-    <t>19.61% (95% CI: [14.07%, 25.14%])</t>
-  </si>
-  <si>
-    <t>22.95% (95% CI: [14.77%, 31.12%])</t>
-  </si>
-  <si>
-    <t>95.17% (95% CI: [94.22%, 96.13%])</t>
-  </si>
-  <si>
-    <t>33.29% (95% CI: [19.76%, 46.83%])</t>
-  </si>
-  <si>
-    <t>27.28% (95% CI: [14.66%, 39.91%])</t>
-  </si>
-  <si>
-    <t>95.47% (95% CI: [95.02%, 95.91%])</t>
-  </si>
-  <si>
-    <t>33.23% (95% CI: [19.26%, 47.21%])</t>
-  </si>
-  <si>
-    <t>33.54% (95% CI: [18.45%, 48.63%])</t>
-  </si>
-  <si>
-    <t>95.02% (95% CI: [94.63%, 95.42%])</t>
-  </si>
-  <si>
-    <t>44.56% (95% CI: [25.59%, 63.53%])</t>
-  </si>
-  <si>
-    <t>15.62% (95% CI: [5.69%, 25.55%])</t>
-  </si>
-  <si>
-    <t>95.35% (95% CI: [95.15%, 95.55%])</t>
-  </si>
-  <si>
-    <t>54.75% (95% CI: [37.71%, 71.79%])</t>
-  </si>
-  <si>
-    <t>20.89% (95% CI: [6.32%, 35.45%])</t>
-  </si>
-  <si>
-    <t>96.37% (95% CI: [95.98%, 96.76%])</t>
-  </si>
-  <si>
-    <t>49.66% (95% CI: [30.48%, 68.84%])</t>
-  </si>
-  <si>
-    <t>32.38% (95% CI: [13.54%, 51.22%])</t>
-  </si>
-  <si>
-    <t>95.38% (95% CI: [95.10%, 95.67%])</t>
-  </si>
-  <si>
-    <t>39.76% (95% CI: [23.22%, 56.29%])</t>
-  </si>
-  <si>
-    <t>34.15% (95% CI: [21.35%, 46.95%])</t>
-  </si>
-  <si>
-    <t>93.47% (95% CI: [92.77%, 94.16%])</t>
-  </si>
-  <si>
-    <t>21.55% (95% CI: [13.38%, 29.72%])</t>
-  </si>
-  <si>
-    <t>19.55% (95% CI: [10.95%, 28.16%])</t>
-  </si>
-  <si>
-    <t>94.22% (95% CI: [93.77%, 94.68%])</t>
-  </si>
-  <si>
-    <t>29.30% (95% CI: [19.98%, 38.62%])</t>
-  </si>
-  <si>
-    <t>26.19% (95% CI: [12.85%, 39.52%])</t>
-  </si>
-  <si>
-    <t>94.38% (95% CI: [93.81%, 94.95%])</t>
-  </si>
-  <si>
-    <t>30.53% (95% CI: [5.83%, 55.23%])</t>
-  </si>
-  <si>
-    <t>22.15% (95% CI: [11.79%, 32.51%])</t>
-  </si>
-  <si>
-    <t>95.01% (95% CI: [94.50%, 95.52%])</t>
-  </si>
-  <si>
-    <t>38.49% (95% CI: [18.99%, 57.98%])</t>
-  </si>
-  <si>
-    <t>14.97% (95% CI: [8.93%, 21.01%])</t>
-  </si>
-  <si>
-    <t>95.88% (95% CI: [95.11%, 96.66%])</t>
-  </si>
-  <si>
-    <t>39.27% (95% CI: [15.08%, 63.46%])</t>
-  </si>
-  <si>
-    <t>23.57% (95% CI: [-0.71%, 47.85%])</t>
-  </si>
-  <si>
-    <t>95.37% (95% CI: [94.58%, 96.15%])</t>
-  </si>
-  <si>
-    <t>59.22% (95% CI: [21.24%, 97.20%])</t>
-  </si>
-  <si>
-    <t>12.63% (95% CI: [7.20%, 18.06%])</t>
-  </si>
-  <si>
-    <t>Classification Comparison (Confidence [95% CI])</t>
-  </si>
-  <si>
-    <t>78.49% (95% CI: [64.62%, 92.35%])</t>
-  </si>
-  <si>
-    <t>25.04% (95% CI: [14.58%, 35.51%])</t>
-  </si>
-  <si>
-    <t>18.88% (95% CI: [10.68%, 27.07%])</t>
-  </si>
-  <si>
-    <t>99.56% (95% CI: [99.21%, 99.92%])</t>
-  </si>
-  <si>
-    <t>41.95% (95% CI: [39.85%, 44.05%])</t>
-  </si>
-  <si>
-    <t>37.52% (95% CI: [35.59%, 39.46%]</t>
-  </si>
-  <si>
-    <t>97.61% (95% CI: [95.94%, 99.28%])</t>
-  </si>
-  <si>
-    <t>16.00% (95% CI: [13.74%, 18.26%])</t>
-  </si>
-  <si>
-    <t>16.22% (95% CI: [13.31%, 19.12%])</t>
-  </si>
-  <si>
-    <t>99.87% (95% CI: [99.76%, 99.98%])</t>
-  </si>
-  <si>
-    <t>26.36% (95% CI: [24.77%, 27.95%])</t>
-  </si>
-  <si>
-    <t>37.94% (95% CI: [36.44%, 39.44%])</t>
-  </si>
-  <si>
     <t>Pancreas (Mouse model)</t>
-  </si>
-  <si>
-    <t>98.40% (95% CI: [98.20%, 98.59%])</t>
-  </si>
-  <si>
-    <t>34.47% (95% CI: [27.90%, 41.05%])</t>
-  </si>
-  <si>
-    <t>33.03% (95% CI: [25.50%, 40.57%])</t>
   </si>
   <si>
     <t>Index</t>
@@ -406,6 +192,60 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [65.55%, 99.48%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [68.78%, 99.39%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [66.55%, 99.48%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [67.27%, 99.43%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: 63.56%, 99.52%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [55.21%, 99.66%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [63.56%, 99.52%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [70.12%, 99.35%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [58.50%, 99.61%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [46.15%, 99.76%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [51.19%, 99.71%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [81.56%, 98.79%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [93.17%, 96.36%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [72.37%, 99.28%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [92.62%, 96.64%])</t>
+  </si>
+  <si>
+    <t>95.00% (95% CI: [91.55%, 97.09%])</t>
+  </si>
+  <si>
+    <t>Cross-Modal Segmentation Performance (95% Wilson Score Intervals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioVision - Segmentation Accuracy </t>
   </si>
 </sst>
 </file>
@@ -536,7 +376,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -589,16 +429,22 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -612,9 +458,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -952,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E31BC63-FA3A-471A-9E02-568C0CB41883}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" bestFit="1" customWidth="1"/>
@@ -971,35 +814,35 @@
         <v>0</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
+      <c r="A2" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
       <c r="F2" s="6" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
       <c r="F3" s="6" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1022,7 +865,7 @@
       <c r="A5" s="7">
         <v>2</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="26" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -1040,7 +883,7 @@
       <c r="A6" s="7">
         <v>3</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
@@ -1056,7 +899,7 @@
       <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="24"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
@@ -1072,7 +915,7 @@
       <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="24"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
@@ -1088,7 +931,7 @@
       <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="24"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
@@ -1104,7 +947,7 @@
       <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="9" t="s">
         <v>16</v>
       </c>
@@ -1120,12 +963,12 @@
       <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="24"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="E11" s="10">
         <v>461</v>
@@ -1138,12 +981,12 @@
       <c r="A12" s="7">
         <v>9</v>
       </c>
-      <c r="B12" s="24"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="E12" s="8">
         <v>490</v>
@@ -1156,7 +999,7 @@
       <c r="A13" s="7">
         <v>10</v>
       </c>
-      <c r="B13" s="24"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="9" t="s">
         <v>19</v>
       </c>
@@ -1172,7 +1015,7 @@
       <c r="A14" s="7">
         <v>11</v>
       </c>
-      <c r="B14" s="24"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="9" t="s">
         <v>20</v>
       </c>
@@ -1188,7 +1031,7 @@
       <c r="A15" s="7">
         <v>12</v>
       </c>
-      <c r="B15" s="24"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
@@ -1204,7 +1047,7 @@
       <c r="A16" s="7">
         <v>13</v>
       </c>
-      <c r="B16" s="24"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="9" t="s">
         <v>22</v>
       </c>
@@ -1220,7 +1063,7 @@
       <c r="A17" s="7">
         <v>14</v>
       </c>
-      <c r="B17" s="24"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="9" t="s">
         <v>23</v>
       </c>
@@ -1236,7 +1079,7 @@
       <c r="A18" s="7">
         <v>15</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
@@ -1252,12 +1095,12 @@
       <c r="A19" s="7">
         <v>16</v>
       </c>
-      <c r="B19" s="24"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="9" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="E19" s="10">
         <v>1656</v>
@@ -1270,12 +1113,12 @@
       <c r="A20" s="7">
         <v>17</v>
       </c>
-      <c r="B20" s="24"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="23" t="s">
-        <v>100</v>
+      <c r="D20" s="25" t="s">
+        <v>36</v>
       </c>
       <c r="E20" s="15">
         <v>37695</v>
@@ -1294,7 +1137,7 @@
       <c r="C21" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="23"/>
+      <c r="D21" s="25"/>
       <c r="E21" s="8">
         <v>846</v>
       </c>
@@ -1312,7 +1155,7 @@
       <c r="C22" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="23"/>
+      <c r="D22" s="25"/>
       <c r="E22" s="15">
         <v>4488</v>
       </c>
@@ -1330,7 +1173,7 @@
       <c r="C23" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="23"/>
+      <c r="D23" s="25"/>
       <c r="E23" s="15">
         <v>13059</v>
       </c>
@@ -1339,332 +1182,231 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E24" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="27">
+      <c r="E24" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="19">
         <f>AVERAGE(F4:F23)</f>
         <v>0.98579500000000009</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
-      <c r="B26" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-    </row>
-    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="B26" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+    </row>
+    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="17">
         <v>1</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>30</v>
-      </c>
+      <c r="B28" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="17">
         <v>2</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>33</v>
-      </c>
+      <c r="B29" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="17">
         <v>3</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>36</v>
-      </c>
+      <c r="B30" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="17">
         <v>4</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="18" t="s">
+      <c r="B31" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="18" t="s">
-        <v>39</v>
-      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="17">
         <v>5</v>
       </c>
-      <c r="B32" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="18" t="s">
+      <c r="B32" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="17">
         <v>6</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>45</v>
-      </c>
+      <c r="B33" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="17">
         <v>7</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>48</v>
-      </c>
+      <c r="B34" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="17">
         <v>8</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>51</v>
-      </c>
+      <c r="B35" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="17">
         <v>9</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>54</v>
-      </c>
+      <c r="B36" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="17">
         <v>10</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>57</v>
-      </c>
+      <c r="B37" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="17">
         <v>11</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>60</v>
-      </c>
+      <c r="B38" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="17">
         <v>12</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>63</v>
-      </c>
+      <c r="B39" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="17">
         <v>13</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>66</v>
-      </c>
+      <c r="B40" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="17">
         <v>14</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>69</v>
-      </c>
+      <c r="B41" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="17">
         <v>15</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>72</v>
-      </c>
+      <c r="B42" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="17">
         <v>16</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>89</v>
-      </c>
+      <c r="B43" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="17">
         <v>17</v>
       </c>
-      <c r="B44" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>85</v>
-      </c>
+      <c r="B44" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="17">
         <v>18</v>
       </c>
-      <c r="B45" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>76</v>
-      </c>
+      <c r="B45" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="17">
         <v>19</v>
       </c>
-      <c r="B46" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>79</v>
-      </c>
+      <c r="B46" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="17">
         <v>20</v>
       </c>
-      <c r="B47" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B50" s="20" t="str" cm="1">
-        <f t="array" ref="B50">TEXT(AVERAGE(VALUE(LEFT(B28:B47,FIND("%",B28:B47)-1))),"0.00")&amp;"% (95% CI: ["&amp;TEXT(AVERAGE(VALUE(MID(B28:B47,FIND("[",B28:B47)+1,FIND("%",B28:B47,FIND("[",B28:B47))-FIND("[",B28:B47)-1))),"0.00")&amp;"%, "&amp;TEXT(AVERAGE(VALUE(MID(B28:B47,FIND(", ",B28:B47,FIND("[",B28:B47))+2,FIND("%]",B28:B47)-FIND(", ",B28:B47,FIND("[",B28:B47))-2))),"0.00")&amp;"%])"</f>
-        <v>94.79% (95% CI: [93.51%, 96.08%])</v>
-      </c>
-      <c r="C50" s="20" t="str" cm="1">
-        <f t="array" ref="C50">TEXT(AVERAGE(VALUE(LEFT(C28:C47,FIND("%",C28:C47)-1))),"0.00")&amp;"% (95% CI: ["&amp;TEXT(AVERAGE(VALUE(MID(C28:C47,FIND("[",C28:C47)+1,FIND("%",C28:C47,FIND("[",C28:C47))-FIND("[",C28:C47)-1))),"0.00")&amp;"%, "&amp;TEXT(AVERAGE(VALUE(MID(C28:C47,FIND(", ",C28:C47,FIND("[",C28:C47))+2,FIND("%]",C28:C47)-FIND(", ",C28:C47,FIND("[",C28:C47))-2))),"0.00")&amp;"%])"</f>
-        <v>36.55% (95% CI: [22.71%, 50.40%])</v>
-      </c>
-      <c r="D50" s="20" t="str" cm="1">
-        <f t="array" ref="D50">TEXT(AVERAGE(VALUE(LEFT(D28:D47,FIND("%",D28:D47)-1))),"0.00")&amp;"% (95% CI: ["&amp;TEXT(AVERAGE(VALUE(MID(D28:D47,FIND("[",D28:D47)+1,FIND("%",D28:D47,FIND("[",D28:D47))-FIND("[",D28:D47)-1))),"0.00")&amp;"%, "&amp;TEXT(AVERAGE(VALUE(MID(D28:D47,FIND(", ",D28:D47,FIND("[",D28:D47))+2,FIND("%]",D28:D47)-FIND(", ",D28:D47,FIND("[",D28:D47))-2))),"0.00")&amp;"%])"</f>
-        <v>25.04% (95% CI: [14.95%, 35.13%])</v>
-      </c>
+      <c r="B47" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="8">
